--- a/src/main/resources/TestData.xlsx
+++ b/src/main/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vsgov\eclipse-workspace\LetCodeAutomation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8098A1C8-CEC9-4CE8-B4F3-F3B2A3BA4D71}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{A4462E90-329F-43D1-B6B8-BBF274E99CD2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="1" firstSheet="1" windowHeight="15720" windowWidth="29040" xWindow="-120" xr2:uid="{B7A3B544-B68F-4270-8AEF-7BC8F162F16A}" yWindow="-120"/>
+    <workbookView windowHeight="15720" windowWidth="29040" xWindow="-120" xr2:uid="{B7A3B544-B68F-4270-8AEF-7BC8F162F16A}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="InputTest" r:id="rId1" sheetId="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
   <si>
     <t>FullName</t>
   </si>
@@ -44,9 +44,6 @@
     <t>Selenium</t>
   </si>
   <si>
-    <t>Helena</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
@@ -117,6 +114,21 @@
   </si>
   <si>
     <t>Alert</t>
+  </si>
+  <si>
+    <t>Govind VS</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Java</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Automation</t>
   </si>
 </sst>
 </file>
@@ -161,13 +173,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -483,30 +498,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EDBCFAC-6700-4401-8667-200CAEC1DE16}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="23.140625" collapsed="true"/>
     <col min="2" max="2" customWidth="true" width="21.85546875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" width="25.7109375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" width="15.28515625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" width="19.140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -521,35 +564,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -567,19 +610,19 @@
   <sheetData>
     <row ht="30" r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row customHeight="1" ht="28.5" r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2"/>
     </row>
@@ -603,22 +646,22 @@
   <sheetData>
     <row ht="30" r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1"/>
     </row>
     <row ht="75" r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,16 +684,16 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -668,18 +711,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -705,18 +748,18 @@
   <sheetData>
     <row ht="30" r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row ht="45" r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -734,18 +777,18 @@
   <sheetData>
     <row ht="30" r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row ht="45" r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -760,31 +803,31 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2"/>
     </row>

--- a/src/main/resources/TestData.xlsx
+++ b/src/main/resources/TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vsgov\eclipse-workspace\LetCodeAutomation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{A4462E90-329F-43D1-B6B8-BBF274E99CD2}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{CD1C6732-A450-4FDA-B52D-EB1B23CE773F}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="15720" windowWidth="29040" xWindow="-120" xr2:uid="{B7A3B544-B68F-4270-8AEF-7BC8F162F16A}" yWindow="-120"/>
+    <workbookView activeTab="4" windowHeight="15720" windowWidth="29040" xWindow="-120" xr2:uid="{B7A3B544-B68F-4270-8AEF-7BC8F162F16A}" yWindow="-120"/>
   </bookViews>
   <sheets>
     <sheet name="InputTest" r:id="rId1" sheetId="1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="33">
   <si>
     <t>FullName</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Mens Casual Slim Fit</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
     <t>Govind VS</t>
   </si>
   <si>
@@ -129,6 +126,12 @@
   </si>
   <si>
     <t>Automation</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -520,7 +523,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
@@ -532,10 +535,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -543,10 +546,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -608,7 +611,7 @@
     <col min="1" max="1" customWidth="true" width="18.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
@@ -644,7 +647,7 @@
     <col min="2" max="2" customWidth="true" width="19.5703125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -653,7 +656,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row ht="75" r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row ht="45" r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -676,25 +679,50 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B99087-2C5B-446A-A1D2-2869AB87A74B}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="15.42578125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" width="14.7109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -746,7 +774,7 @@
     <col min="1" max="1" customWidth="true" width="13.85546875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -754,7 +782,7 @@
         <v>6</v>
       </c>
     </row>
-    <row ht="45" r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row ht="30" r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
@@ -775,7 +803,7 @@
     <col min="1" max="1" customWidth="true" width="18.42578125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="30" r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -783,7 +811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row ht="45" r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row ht="30" r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
